--- a/warehouse.xlsx
+++ b/warehouse.xlsx
@@ -6,40 +6,184 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Изделия" r:id="rId3" sheetId="1"/>
-    <sheet name="Группы" r:id="rId4" sheetId="2"/>
+    <sheet name="Оборудование" r:id="rId7" sheetId="51"/>
+    <sheet name="Движение" r:id="rId8" sheetId="52"/>
+    <sheet name="Балтика" r:id="rId9" sheetId="53"/>
+    <sheet name="Склад" r:id="rId10" sheetId="54"/>
+    <sheet name="Скиф" r:id="rId11" sheetId="55"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="9">
-  <si>
-    <t>Название изделия</t>
-  </si>
-  <si>
-    <t>Соседка</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1641" uniqueCount="56">
+  <si>
+    <t>Инвентарный номер</t>
+  </si>
+  <si>
+    <t>Название</t>
+  </si>
+  <si>
+    <t>Серийный номер</t>
+  </si>
+  <si>
+    <t>Количество</t>
+  </si>
+  <si>
+    <t>Статус</t>
+  </si>
+  <si>
+    <t>Группа</t>
+  </si>
+  <si>
+    <t>Объект</t>
+  </si>
+  <si>
+    <t>Комплектность</t>
+  </si>
+  <si>
+    <t>Отсутствует</t>
+  </si>
+  <si>
+    <t>INV-000001</t>
+  </si>
+  <si>
+    <t>Телефон</t>
+  </si>
+  <si>
+    <t>SN-777</t>
+  </si>
+  <si>
+    <t>В группе</t>
+  </si>
+  <si>
+    <t>Балтика</t>
+  </si>
+  <si>
+    <t>Ромашка</t>
+  </si>
+  <si>
+    <t>Комплект</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Тип движения</t>
+  </si>
+  <si>
+    <t>Дата</t>
+  </si>
+  <si>
+    <t>Накладная</t>
+  </si>
+  <si>
+    <t>Источник</t>
+  </si>
+  <si>
+    <t>Получатель</t>
+  </si>
+  <si>
+    <t>Передал</t>
+  </si>
+  <si>
+    <t>Принял</t>
+  </si>
+  <si>
+    <t>Передача</t>
+  </si>
+  <si>
+    <t>30.05.2026</t>
+  </si>
+  <si>
+    <t>НК-125</t>
+  </si>
+  <si>
+    <t>Склад</t>
+  </si>
+  <si>
+    <t>Иванов И.И.</t>
+  </si>
+  <si>
+    <t>Петров П.П.</t>
+  </si>
+  <si>
+    <t>INV-000002</t>
+  </si>
+  <si>
+    <t>На складе</t>
+  </si>
+  <si>
+    <t>Дата получения</t>
+  </si>
+  <si>
+    <t>INV-000003</t>
   </si>
   <si>
     <t>Радиостанция TYT</t>
   </si>
   <si>
-    <t>Телефон</t>
-  </si>
-  <si>
-    <t>Планшет</t>
-  </si>
-  <si>
-    <t>Название группы</t>
-  </si>
-  <si>
-    <t>Склад</t>
+    <t>TYT-001</t>
+  </si>
+  <si>
+    <t>Кокос</t>
+  </si>
+  <si>
+    <t>НК-126</t>
+  </si>
+  <si>
+    <t>Кладовщик</t>
+  </si>
+  <si>
+    <t>Ответственный</t>
+  </si>
+  <si>
+    <t>INV-000004</t>
+  </si>
+  <si>
+    <t>Ноутбук Lenovo</t>
+  </si>
+  <si>
+    <t>LEN-001</t>
   </si>
   <si>
     <t>Скиф</t>
   </si>
   <si>
-    <t>Балтика</t>
+    <t>31.05.2026</t>
+  </si>
+  <si>
+    <t>НК-127</t>
+  </si>
+  <si>
+    <t>НК-130</t>
+  </si>
+  <si>
+    <t>НК-131</t>
+  </si>
+  <si>
+    <t>Возврат</t>
+  </si>
+  <si>
+    <t>НК-132</t>
+  </si>
+  <si>
+    <t>Списано</t>
+  </si>
+  <si>
+    <t>Поступление</t>
+  </si>
+  <si>
+    <t>Списание</t>
+  </si>
+  <si>
+    <t>АКТ-1</t>
+  </si>
+  <si>
+    <t>Комиссия</t>
+  </si>
+  <si>
+    <t>Сломан экран</t>
   </si>
 </sst>
 </file>
@@ -82,34 +226,154 @@
 </styleSheet>
 </file>
 
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
         <v>0</v>
       </c>
+      <c r="B1" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s" s="0">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s" s="0">
+        <v>8</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="D2" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="I2" t="s" s="0">
+        <v>16</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>2</v>
+        <v>30</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="D3" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="I3" t="s" s="0">
+        <v>16</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>3</v>
+        <v>33</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="D4" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="I4" t="s" s="0">
+        <v>16</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>4</v>
+        <v>40</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="D5" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="I5" t="s" s="0">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -117,29 +381,594 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>5</v>
+        <v>17</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C1" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="D1" t="s" s="0">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="F1" t="s" s="0">
+        <v>2</v>
+      </c>
+      <c r="G1" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="H1" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="I1" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="J1" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="K1" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="L1" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="M1" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>8</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>6</v>
+        <v>24</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="G2" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="I2" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="K2" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="L2" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="M2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="N2" t="s" s="0">
+        <v>16</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>7</v>
+        <v>24</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="G3" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="I3" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="K3" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="L3" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="M3" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="N3" t="s" s="0">
+        <v>16</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="G4" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="I4" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="K4" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="L4" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="M4" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="N4" t="s" s="0">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="G5" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="I5" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="J5" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="K5" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="L5" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="M5" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="N5" t="s" s="0">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="G6" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="I6" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="J6" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="K6" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="L6" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="M6" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="N6" t="s" s="0">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="C7" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="G7" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="H7" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="I7" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="J7" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="K7" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="L7" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="M7" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="N7" t="s" s="0">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="C8" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="E8" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F8" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="G8" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="H8" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="I8" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="J8" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="K8" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="L8" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="M8" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="N8" t="s" s="0">
+        <v>55</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="0">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s" s="0">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="F1" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="G1" t="s" s="0">
         <v>8</v>
+      </c>
+      <c r="H1" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="I1" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="D2" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="I2" t="s" s="0">
+        <v>26</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:I3"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="0">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s" s="0">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="F1" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="G1" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="H1" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="I1" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="D2" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="I2" t="s" s="0">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="D3" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="I3" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="0">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s" s="0">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="F1" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="G1" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="H1" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="I1" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="D2" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="I2" t="s" s="0">
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/warehouse.xlsx
+++ b/warehouse.xlsx
@@ -1,22 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr date1904="false"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent>
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\leono\Desktop\Kotlin\warehous\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ED2C952-C80A-4147-9414-42C4BBB6E080}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0"/>
+    <workbookView xWindow="4905" yWindow="1710" windowWidth="25365" windowHeight="18120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Оборудование" r:id="rId7" sheetId="51"/>
-    <sheet name="Движение" r:id="rId8" sheetId="52"/>
-    <sheet name="Балтика" r:id="rId9" sheetId="53"/>
-    <sheet name="Склад" r:id="rId10" sheetId="54"/>
-    <sheet name="Скиф" r:id="rId11" sheetId="55"/>
+    <sheet name="Оборудование" r:id="rId9" sheetId="56"/>
+    <sheet name="Движение" r:id="rId10" sheetId="57"/>
+    <sheet name="Балтика" r:id="rId11" sheetId="58"/>
+    <sheet name="Склад" r:id="rId12" sheetId="59"/>
+    <sheet name="Скиф" r:id="rId13" sheetId="60"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1641" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="55">
   <si>
     <t>Инвентарный номер</t>
   </si>
@@ -111,9 +119,6 @@
     <t>INV-000002</t>
   </si>
   <si>
-    <t>На складе</t>
-  </si>
-  <si>
     <t>Дата получения</t>
   </si>
   <si>
@@ -162,9 +167,6 @@
     <t>НК-131</t>
   </si>
   <si>
-    <t>Возврат</t>
-  </si>
-  <si>
     <t>НК-132</t>
   </si>
   <si>
@@ -184,16 +186,19 @@
   </si>
   <si>
     <t>Сломан экран</t>
+  </si>
+  <si>
+    <t>asd</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color indexed="8"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -205,7 +210,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="darkGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
@@ -223,12 +228,320 @@
   <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+  </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+  <a:themeElements>
+    <a:clrScheme name="Стандартная">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4472C4"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Стандартная">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Стандартная">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
+<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -291,22 +604,22 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>10</v>
+        <v>54</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>11</v>
+        <v>54</v>
       </c>
       <c r="D3" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="E3" t="s" s="0">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="F3" t="s" s="0">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="G3" t="s" s="0">
         <v>16</v>
@@ -315,18 +628,18 @@
         <v>15</v>
       </c>
       <c r="I3" t="s" s="0">
-        <v>16</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D4" t="n" s="0">
         <v>1.0</v>
@@ -335,44 +648,15 @@
         <v>12</v>
       </c>
       <c r="F4" t="s" s="0">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="G4" t="s" s="0">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="H4" t="s" s="0">
         <v>15</v>
       </c>
       <c r="I4" t="s" s="0">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="0">
-        <v>40</v>
-      </c>
-      <c r="B5" t="s" s="0">
-        <v>41</v>
-      </c>
-      <c r="C5" t="s" s="0">
-        <v>42</v>
-      </c>
-      <c r="D5" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="E5" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F5" t="s" s="0">
-        <v>43</v>
-      </c>
-      <c r="G5" t="s" s="0">
-        <v>36</v>
-      </c>
-      <c r="H5" t="s" s="0">
-        <v>15</v>
-      </c>
-      <c r="I5" t="s" s="0">
         <v>16</v>
       </c>
     </row>
@@ -381,7 +665,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:N8"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
@@ -482,16 +766,16 @@
         <v>25</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D3" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="E3" t="s" s="0">
         <v>33</v>
       </c>
-      <c r="E3" t="s" s="0">
+      <c r="F3" t="s" s="0">
         <v>34</v>
-      </c>
-      <c r="F3" t="s" s="0">
-        <v>35</v>
       </c>
       <c r="G3" t="n" s="0">
         <v>1.0</v>
@@ -503,13 +787,13 @@
         <v>13</v>
       </c>
       <c r="J3" t="s" s="0">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K3" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="L3" t="s" s="0">
         <v>38</v>
-      </c>
-      <c r="L3" t="s" s="0">
-        <v>39</v>
       </c>
       <c r="M3" t="s" s="0">
         <v>15</v>
@@ -523,19 +807,19 @@
         <v>24</v>
       </c>
       <c r="B4" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="C4" t="s" s="0">
         <v>44</v>
       </c>
-      <c r="C4" t="s" s="0">
-        <v>45</v>
-      </c>
       <c r="D4" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="E4" t="s" s="0">
         <v>40</v>
       </c>
-      <c r="E4" t="s" s="0">
+      <c r="F4" t="s" s="0">
         <v>41</v>
-      </c>
-      <c r="F4" t="s" s="0">
-        <v>42</v>
       </c>
       <c r="G4" t="n" s="0">
         <v>1.0</v>
@@ -544,16 +828,16 @@
         <v>27</v>
       </c>
       <c r="I4" t="s" s="0">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J4" t="s" s="0">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K4" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="L4" t="s" s="0">
         <v>38</v>
-      </c>
-      <c r="L4" t="s" s="0">
-        <v>39</v>
       </c>
       <c r="M4" t="s" s="0">
         <v>15</v>
@@ -567,19 +851,19 @@
         <v>24</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D5" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="E5" t="s" s="0">
         <v>33</v>
       </c>
-      <c r="E5" t="s" s="0">
+      <c r="F5" t="s" s="0">
         <v>34</v>
-      </c>
-      <c r="F5" t="s" s="0">
-        <v>35</v>
       </c>
       <c r="G5" t="n" s="0">
         <v>1.0</v>
@@ -594,10 +878,10 @@
         <v>16</v>
       </c>
       <c r="K5" t="s" s="0">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L5" t="s" s="0">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M5" t="s" s="0">
         <v>15</v>
@@ -611,19 +895,19 @@
         <v>24</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D6" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="E6" t="s" s="0">
         <v>33</v>
       </c>
-      <c r="E6" t="s" s="0">
+      <c r="F6" t="s" s="0">
         <v>34</v>
-      </c>
-      <c r="F6" t="s" s="0">
-        <v>35</v>
       </c>
       <c r="G6" t="n" s="0">
         <v>1.0</v>
@@ -635,13 +919,13 @@
         <v>13</v>
       </c>
       <c r="J6" t="s" s="0">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K6" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="L6" t="s" s="0">
         <v>38</v>
-      </c>
-      <c r="L6" t="s" s="0">
-        <v>39</v>
       </c>
       <c r="M6" t="s" s="0">
         <v>15</v>
@@ -652,22 +936,22 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D7" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="E7" t="s" s="0">
         <v>33</v>
       </c>
-      <c r="E7" t="s" s="0">
+      <c r="F7" t="s" s="0">
         <v>34</v>
-      </c>
-      <c r="F7" t="s" s="0">
-        <v>35</v>
       </c>
       <c r="G7" t="n" s="0">
         <v>1.0</v>
@@ -682,10 +966,10 @@
         <v>16</v>
       </c>
       <c r="K7" t="s" s="0">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L7" t="s" s="0">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M7" t="s" s="0">
         <v>15</v>
@@ -696,13 +980,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D8" t="s" s="0">
         <v>30</v>
@@ -720,22 +1004,22 @@
         <v>27</v>
       </c>
       <c r="I8" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="J8" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="K8" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="L8" t="s" s="0">
         <v>52</v>
-      </c>
-      <c r="J8" t="s" s="0">
-        <v>16</v>
-      </c>
-      <c r="K8" t="s" s="0">
-        <v>38</v>
-      </c>
-      <c r="L8" t="s" s="0">
-        <v>54</v>
       </c>
       <c r="M8" t="s" s="0">
         <v>15</v>
       </c>
       <c r="N8" t="s" s="0">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -743,7 +1027,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:I2"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
@@ -771,7 +1055,7 @@
         <v>8</v>
       </c>
       <c r="H1" t="s" s="0">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I1" t="s" s="0">
         <v>19</v>
@@ -811,104 +1095,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:I3"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="0">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s" s="0">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s" s="0">
-        <v>6</v>
-      </c>
-      <c r="F1" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="G1" t="s" s="0">
-        <v>8</v>
-      </c>
-      <c r="H1" t="s" s="0">
-        <v>32</v>
-      </c>
-      <c r="I1" t="s" s="0">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="0">
-        <v>30</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="C2" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="D2" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="E2" t="s" s="0">
-        <v>16</v>
-      </c>
-      <c r="F2" t="s" s="0">
-        <v>15</v>
-      </c>
-      <c r="G2" t="s" s="0">
-        <v>16</v>
-      </c>
-      <c r="H2" t="s" s="0">
-        <v>44</v>
-      </c>
-      <c r="I2" t="s" s="0">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="0">
-        <v>33</v>
-      </c>
-      <c r="B3" t="s" s="0">
-        <v>34</v>
-      </c>
-      <c r="C3" t="s" s="0">
-        <v>35</v>
-      </c>
-      <c r="D3" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="E3" t="s" s="0">
-        <v>16</v>
-      </c>
-      <c r="F3" t="s" s="0">
-        <v>15</v>
-      </c>
-      <c r="G3" t="s" s="0">
-        <v>16</v>
-      </c>
-      <c r="H3" t="s" s="0">
-        <v>44</v>
-      </c>
-      <c r="I3" t="s" s="0">
-        <v>49</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:I2"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
@@ -936,7 +1123,7 @@
         <v>8</v>
       </c>
       <c r="H1" t="s" s="0">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I1" t="s" s="0">
         <v>19</v>
@@ -944,31 +1131,99 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="D2" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="E2" t="s" s="0">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="F2" t="s" s="0">
         <v>15</v>
       </c>
       <c r="G2" t="s" s="0">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="H2" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="I2" t="s" s="0">
+        <v>47</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet60.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="0">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s" s="0">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="F1" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="G1" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="H1" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="I1" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="D2" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="I2" t="s" s="0">
         <v>44</v>
-      </c>
-      <c r="I2" t="s" s="0">
-        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/warehouse.xlsx
+++ b/warehouse.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>Ключ</t>
   </si>
@@ -23,13 +23,13 @@
     <t>warehouseTitle</t>
   </si>
   <si>
-    <t>Лабораторная</t>
+    <t>Склад</t>
   </si>
   <si>
     <t>equipmentTitle</t>
   </si>
   <si>
-    <t>Оборудка</t>
+    <t>Оборудование</t>
   </si>
   <si>
     <t>groupTitle</t>
@@ -41,10 +41,7 @@
     <t>locationTitle</t>
   </si>
   <si>
-    <t>Пост</t>
-  </si>
-  <si>
-    <t>Лаборатория</t>
+    <t>Объект</t>
   </si>
 </sst>
 </file>
@@ -105,7 +102,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">

--- a/warehouse.xlsx
+++ b/warehouse.xlsx
@@ -7,12 +7,18 @@
   </bookViews>
   <sheets>
     <sheet name="Настройки" r:id="rId3" sheetId="1"/>
+    <sheet name="Склад" r:id="rId10" sheetId="26"/>
+    <sheet name="Оборудование" r:id="rId9" sheetId="33"/>
+    <sheet name="Движение" r:id="rId8" sheetId="34"/>
+    <sheet name="Скиф" r:id="rId11" sheetId="35"/>
+    <sheet name="Балтика" r:id="rId12" sheetId="36"/>
+    <sheet name="Подразделения" r:id="rId13" sheetId="37"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="56">
   <si>
     <t>Ключ</t>
   </si>
@@ -42,6 +48,144 @@
   </si>
   <si>
     <t>Объект</t>
+  </si>
+  <si>
+    <t>Инвентарный номер</t>
+  </si>
+  <si>
+    <t>Название</t>
+  </si>
+  <si>
+    <t>Серийный номер</t>
+  </si>
+  <si>
+    <t>Количество</t>
+  </si>
+  <si>
+    <t>Статус</t>
+  </si>
+  <si>
+    <t>Группа</t>
+  </si>
+  <si>
+    <t>Комплектность</t>
+  </si>
+  <si>
+    <t>Отсутствует</t>
+  </si>
+  <si>
+    <t>INV-000001</t>
+  </si>
+  <si>
+    <t>Кабель</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>На складе</t>
+  </si>
+  <si>
+    <t>Комплект</t>
+  </si>
+  <si>
+    <t>Тип движения</t>
+  </si>
+  <si>
+    <t>Дата</t>
+  </si>
+  <si>
+    <t>Накладная</t>
+  </si>
+  <si>
+    <t>Источник</t>
+  </si>
+  <si>
+    <t>Получатель</t>
+  </si>
+  <si>
+    <t>Передал</t>
+  </si>
+  <si>
+    <t>Принял</t>
+  </si>
+  <si>
+    <t>Дата получения</t>
+  </si>
+  <si>
+    <t>INV-000002</t>
+  </si>
+  <si>
+    <t>В группе</t>
+  </si>
+  <si>
+    <t>Скиф</t>
+  </si>
+  <si>
+    <t>Кокос</t>
+  </si>
+  <si>
+    <t>Передача</t>
+  </si>
+  <si>
+    <t>02.06.2026</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>Кладовщик</t>
+  </si>
+  <si>
+    <t>Ответственный</t>
+  </si>
+  <si>
+    <t>INV-000003</t>
+  </si>
+  <si>
+    <t>Балтика</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>INV-000004</t>
+  </si>
+  <si>
+    <t>03.06.2026</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>INV-000005</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>Смирнов А.В.</t>
+  </si>
+  <si>
+    <t>Иванов В.Г.</t>
+  </si>
+  <si>
+    <t>Банан</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>Иванов</t>
+  </si>
+  <si>
+    <t>Петров</t>
+  </si>
+  <si>
+    <t>Тест</t>
   </si>
 </sst>
 </file>
@@ -132,4 +276,827 @@
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="C1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="D1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="E1" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="G1" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="H1" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="I1" t="s" s="0">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="D2" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="I2" t="s" s="0">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="C1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="D1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="E1" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="F1" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="G1" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="H1" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="I1" t="s" s="0">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="D2" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="I2" t="s" s="0">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="D3" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="I3" t="s" s="0">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="D4" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="I4" t="s" s="0">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="D5" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="I5" t="s" s="0">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="D6" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="I6" t="s" s="0">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:N7"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="C1" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="D1" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="E1" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="F1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="G1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="H1" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="I1" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="J1" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="L1" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="M1" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="G2" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="I2" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="K2" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="L2" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="M2" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N2" t="s" s="0">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="G3" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="I3" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="K3" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="L3" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="M3" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N3" t="s" s="0">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="G4" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="I4" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="K4" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="L4" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="M4" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N4" t="s" s="0">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="G5" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="I5" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="J5" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="K5" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="L5" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="M5" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N5" t="s" s="0">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="G6" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="I6" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="J6" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="K6" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="L6" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="M6" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N6" t="s" s="0">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="C7" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="G7" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="H7" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="I7" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="J7" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="K7" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="L7" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="M7" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N7" t="s" s="0">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="C1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="D1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="E1" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="G1" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="H1" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="I1" t="s" s="0">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="D2" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="I2" t="s" s="0">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="D3" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="I3" t="s" s="0">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="D4" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="I4" t="s" s="0">
+        <v>46</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:I3"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="C1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="D1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="E1" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="G1" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="H1" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="I1" t="s" s="0">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="D2" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="I2" t="s" s="0">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="D3" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="I3" t="s" s="0">
+        <v>48</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:A4"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>41</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>
--- a/warehouse.xlsx
+++ b/warehouse.xlsx
@@ -8,17 +8,19 @@
   <sheets>
     <sheet name="Настройки" r:id="rId3" sheetId="1"/>
     <sheet name="Склад" r:id="rId10" sheetId="26"/>
-    <sheet name="Оборудование" r:id="rId9" sheetId="33"/>
-    <sheet name="Движение" r:id="rId8" sheetId="34"/>
-    <sheet name="Скиф" r:id="rId11" sheetId="35"/>
-    <sheet name="Балтика" r:id="rId12" sheetId="36"/>
-    <sheet name="Подразделения" r:id="rId13" sheetId="37"/>
+    <sheet name="Оборудование" r:id="rId16" sheetId="67"/>
+    <sheet name="Движение" r:id="rId14" sheetId="68"/>
+    <sheet name="Скиф" r:id="rId11" sheetId="69"/>
+    <sheet name="Балтика" r:id="rId12" sheetId="70"/>
+    <sheet name="Тест" r:id="rId17" sheetId="71"/>
+    <sheet name="Подразделения" r:id="rId13" sheetId="72"/>
+    <sheet name="Объекты" r:id="rId15" sheetId="73"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2546" uniqueCount="60">
   <si>
     <t>Ключ</t>
   </si>
@@ -186,6 +188,18 @@
   </si>
   <si>
     <t>Тест</t>
+  </si>
+  <si>
+    <t>05.06.2026</t>
+  </si>
+  <si>
+    <t>Ромашка</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>9</t>
   </si>
 </sst>
 </file>
@@ -346,7 +360,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet67.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
@@ -513,7 +527,7 @@
         <v>32</v>
       </c>
       <c r="F6" t="s" s="0">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="G6" t="s" s="0">
         <v>20</v>
@@ -530,9 +544,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet68.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -843,12 +857,144 @@
         <v>20</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="C8" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="E8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="F8" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="G8" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="H8" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="I8" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="J8" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="K8" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="L8" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="M8" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N8" t="s" s="0">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="C9" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="D9" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="E9" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="F9" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="G9" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="H9" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="I9" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="J9" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="K9" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="L9" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="M9" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N9" t="s" s="0">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="C10" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="D10" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="E10" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="F10" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="G10" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="H10" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="I10" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="J10" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="K10" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="L10" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="M10" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N10" t="s" s="0">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet69.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:I4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
@@ -963,10 +1109,10 @@
         <v>20</v>
       </c>
       <c r="H4" t="s" s="0">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="I4" t="s" s="0">
-        <v>46</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -974,9 +1120,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet70.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1037,41 +1183,80 @@
         <v>45</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="s" s="0">
-        <v>47</v>
-      </c>
-      <c r="B3" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="C3" t="s" s="0">
-        <v>20</v>
-      </c>
-      <c r="D3" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="E3" t="s" s="0">
-        <v>20</v>
-      </c>
-      <c r="F3" t="s" s="0">
-        <v>22</v>
-      </c>
-      <c r="G3" t="s" s="0">
-        <v>20</v>
-      </c>
-      <c r="H3" t="s" s="0">
-        <v>44</v>
-      </c>
-      <c r="I3" t="s" s="0">
-        <v>48</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet71.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="C1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="D1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="E1" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="G1" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="H1" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="I1" t="s" s="0">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="D2" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="I2" t="s" s="0">
+        <v>59</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet72.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:A4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
@@ -1099,4 +1284,34 @@
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet73.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:A4"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>57</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>